--- a/Are Prices Justified - IPL 2026/_dataset/IPL_2026_Combined_Data.xlsx
+++ b/Are Prices Justified - IPL 2026/_dataset/IPL_2026_Combined_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rano's PC\Machine\InsightForge\InsightForge\Are Prices Justified - IPL 2026\_dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60176F27-0518-4398-B4C1-9301C5C33087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000351AC-2844-4174-AB2C-9C9473208A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="512">
   <si>
     <t>POS</t>
   </si>
@@ -1558,6 +1558,9 @@
   </si>
   <si>
     <t xml:space="preserve">Xavier Bartlett  </t>
+  </si>
+  <si>
+    <t>Rajasthan Royals</t>
   </si>
 </sst>
 </file>
@@ -14453,7 +14456,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
@@ -18991,6 +18994,121 @@
         <v>328</v>
       </c>
     </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175">
+        <v>2025</v>
+      </c>
+      <c r="C175" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="D175" s="2">
+        <v>11000000</v>
+      </c>
+      <c r="E175" t="s">
+        <v>408</v>
+      </c>
+      <c r="F175" t="s">
+        <v>511</v>
+      </c>
+      <c r="G175" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>31</v>
+      </c>
+      <c r="B176">
+        <v>2025</v>
+      </c>
+      <c r="C176" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="D176" s="2">
+        <v>210000000</v>
+      </c>
+      <c r="E176" t="s">
+        <v>408</v>
+      </c>
+      <c r="F176" t="s">
+        <v>411</v>
+      </c>
+      <c r="G176" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>131</v>
+      </c>
+      <c r="B177">
+        <v>2025</v>
+      </c>
+      <c r="C177" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="D177" s="2">
+        <v>163000000</v>
+      </c>
+      <c r="E177" t="s">
+        <v>408</v>
+      </c>
+      <c r="F177" t="s">
+        <v>440</v>
+      </c>
+      <c r="G177" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>141</v>
+      </c>
+      <c r="B178">
+        <v>2025</v>
+      </c>
+      <c r="C178" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="D178" s="2">
+        <v>180000000</v>
+      </c>
+      <c r="E178" t="s">
+        <v>408</v>
+      </c>
+      <c r="F178" t="s">
+        <v>511</v>
+      </c>
+      <c r="G178" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>220</v>
+      </c>
+      <c r="B179">
+        <v>2025</v>
+      </c>
+      <c r="C179" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="D179" s="2">
+        <v>120000000</v>
+      </c>
+      <c r="E179" t="s">
+        <v>408</v>
+      </c>
+      <c r="F179" t="s">
+        <v>418</v>
+      </c>
+      <c r="G179" t="s">
+        <v>415</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="G1:G174" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Are Prices Justified - IPL 2026/_dataset/IPL_2026_Combined_Data.xlsx
+++ b/Are Prices Justified - IPL 2026/_dataset/IPL_2026_Combined_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rano's PC\Machine\InsightForge\InsightForge\Are Prices Justified - IPL 2026\_dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000351AC-2844-4174-AB2C-9C9473208A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20741EBE-19A5-4C00-A0EB-1A560FAED0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1940" uniqueCount="516">
   <si>
     <t>POS</t>
   </si>
@@ -1561,14 +1561,34 @@
   </si>
   <si>
     <t>Rajasthan Royals</t>
+  </si>
+  <si>
+    <t>cricket_role</t>
+  </si>
+  <si>
+    <t>Batters</t>
+  </si>
+  <si>
+    <t>Bowlers</t>
+  </si>
+  <si>
+    <t>All Rounders</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1596,10 +1616,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14456,7 +14482,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:K179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
@@ -14467,10 +14493,11 @@
     <col min="6" max="6" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -14495,8 +14522,12 @@
       <c r="H1" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>512</v>
+      </c>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>182</v>
       </c>
@@ -14521,8 +14552,11 @@
       <c r="H2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>373</v>
       </c>
@@ -14547,8 +14581,11 @@
       <c r="H3" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -14573,8 +14610,11 @@
       <c r="H4" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>286</v>
       </c>
@@ -14599,8 +14639,11 @@
       <c r="H5" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>147</v>
       </c>
@@ -14625,8 +14668,11 @@
       <c r="H6" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -14651,8 +14697,11 @@
       <c r="H7" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>370</v>
       </c>
@@ -14677,8 +14726,11 @@
       <c r="H8" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>270</v>
       </c>
@@ -14703,8 +14755,11 @@
       <c r="H9" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>229</v>
       </c>
@@ -14729,8 +14784,11 @@
       <c r="H10" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -14755,8 +14813,11 @@
       <c r="H11" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>195</v>
       </c>
@@ -14781,8 +14842,11 @@
       <c r="H12" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>205</v>
       </c>
@@ -14807,8 +14871,11 @@
       <c r="H13" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>211</v>
       </c>
@@ -14833,8 +14900,11 @@
       <c r="H14" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>273</v>
       </c>
@@ -14859,8 +14929,11 @@
       <c r="H15" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>293</v>
       </c>
@@ -14885,8 +14958,11 @@
       <c r="H16" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>241</v>
       </c>
@@ -14911,8 +14987,11 @@
       <c r="H17" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>297</v>
       </c>
@@ -14937,8 +15016,11 @@
       <c r="H18" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>165</v>
       </c>
@@ -14963,8 +15045,11 @@
       <c r="H19" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>298</v>
       </c>
@@ -14989,8 +15074,11 @@
       <c r="H20" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>267</v>
       </c>
@@ -15015,8 +15103,11 @@
       <c r="H21" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>164</v>
       </c>
@@ -15041,8 +15132,11 @@
       <c r="H22" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>152</v>
       </c>
@@ -15067,8 +15161,11 @@
       <c r="H23" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>210</v>
       </c>
@@ -15093,8 +15190,11 @@
       <c r="H24" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>396</v>
       </c>
@@ -15119,8 +15219,11 @@
       <c r="H25" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>221</v>
       </c>
@@ -15145,8 +15248,11 @@
       <c r="H26" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>290</v>
       </c>
@@ -15171,8 +15277,11 @@
       <c r="H27" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>113</v>
       </c>
@@ -15197,8 +15306,11 @@
       <c r="H28" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>77</v>
       </c>
@@ -15223,8 +15335,11 @@
       <c r="H29" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>291</v>
       </c>
@@ -15249,8 +15364,11 @@
       <c r="H30" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>154</v>
       </c>
@@ -15275,8 +15393,11 @@
       <c r="H31" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>232</v>
       </c>
@@ -15301,8 +15422,11 @@
       <c r="H32" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>82</v>
       </c>
@@ -15327,8 +15451,11 @@
       <c r="H33" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>171</v>
       </c>
@@ -15353,8 +15480,11 @@
       <c r="H34" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -15379,8 +15509,11 @@
       <c r="H35" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>292</v>
       </c>
@@ -15405,8 +15538,11 @@
       <c r="H36" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>391</v>
       </c>
@@ -15431,8 +15567,11 @@
       <c r="H37" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>117</v>
       </c>
@@ -15457,8 +15596,11 @@
       <c r="H38" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>263</v>
       </c>
@@ -15483,8 +15625,11 @@
       <c r="H39" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>106</v>
       </c>
@@ -15509,8 +15654,11 @@
       <c r="H40" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>198</v>
       </c>
@@ -15535,8 +15683,11 @@
       <c r="H41" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>366</v>
       </c>
@@ -15561,8 +15712,11 @@
       <c r="H42" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>157</v>
       </c>
@@ -15587,8 +15741,11 @@
       <c r="H43" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>272</v>
       </c>
@@ -15613,8 +15770,11 @@
       <c r="H44" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>254</v>
       </c>
@@ -15639,8 +15799,11 @@
       <c r="H45" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I45" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>36</v>
       </c>
@@ -15665,8 +15828,11 @@
       <c r="H46" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>187</v>
       </c>
@@ -15691,8 +15857,11 @@
       <c r="H47" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>40</v>
       </c>
@@ -15717,8 +15886,11 @@
       <c r="H48" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>186</v>
       </c>
@@ -15743,8 +15915,11 @@
       <c r="H49" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I49" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>350</v>
       </c>
@@ -15769,8 +15944,11 @@
       <c r="H50" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I50" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>174</v>
       </c>
@@ -15795,8 +15973,11 @@
       <c r="H51" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I51" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>199</v>
       </c>
@@ -15821,8 +16002,11 @@
       <c r="H52" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>259</v>
       </c>
@@ -15847,8 +16031,11 @@
       <c r="H53" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I53" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>280</v>
       </c>
@@ -15873,8 +16060,11 @@
       <c r="H54" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I54" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>184</v>
       </c>
@@ -15899,8 +16089,11 @@
       <c r="H55" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I55" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>201</v>
       </c>
@@ -15925,8 +16118,11 @@
       <c r="H56" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I56" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -15951,8 +16147,11 @@
       <c r="H57" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I57" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>317</v>
       </c>
@@ -15977,8 +16176,11 @@
       <c r="H58" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I58" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>139</v>
       </c>
@@ -16003,8 +16205,11 @@
       <c r="H59" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I59" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>45</v>
       </c>
@@ -16029,8 +16234,11 @@
       <c r="H60" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I60" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>217</v>
       </c>
@@ -16055,8 +16263,11 @@
       <c r="H61" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I61" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>129</v>
       </c>
@@ -16081,8 +16292,11 @@
       <c r="H62" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I62" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>252</v>
       </c>
@@ -16107,8 +16321,11 @@
       <c r="H63" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I63" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>240</v>
       </c>
@@ -16133,8 +16350,11 @@
       <c r="H64" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I64" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>374</v>
       </c>
@@ -16159,8 +16379,11 @@
       <c r="H65" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I65" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>148</v>
       </c>
@@ -16185,8 +16408,11 @@
       <c r="H66" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I66" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>256</v>
       </c>
@@ -16211,8 +16437,11 @@
       <c r="H67" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I67" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>239</v>
       </c>
@@ -16237,8 +16466,11 @@
       <c r="H68" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I68" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>250</v>
       </c>
@@ -16263,8 +16495,11 @@
       <c r="H69" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I69" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>245</v>
       </c>
@@ -16289,8 +16524,11 @@
       <c r="H70" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I70" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>399</v>
       </c>
@@ -16315,8 +16553,11 @@
       <c r="H71" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I71" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>281</v>
       </c>
@@ -16341,8 +16582,11 @@
       <c r="H72" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I72" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>356</v>
       </c>
@@ -16367,8 +16611,11 @@
       <c r="H73" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I73" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>238</v>
       </c>
@@ -16393,8 +16640,11 @@
       <c r="H74" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I74" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>379</v>
       </c>
@@ -16419,8 +16669,11 @@
       <c r="H75" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I75" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>197</v>
       </c>
@@ -16445,8 +16698,11 @@
       <c r="H76" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I76" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>213</v>
       </c>
@@ -16471,8 +16727,11 @@
       <c r="H77" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I77" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>150</v>
       </c>
@@ -16497,8 +16756,11 @@
       <c r="H78" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I78" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>262</v>
       </c>
@@ -16523,8 +16785,11 @@
       <c r="H79" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I79" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>204</v>
       </c>
@@ -16549,8 +16814,11 @@
       <c r="H80" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I80" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>274</v>
       </c>
@@ -16575,8 +16843,11 @@
       <c r="H81" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I81" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>54</v>
       </c>
@@ -16601,8 +16872,11 @@
       <c r="H82" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I82" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>231</v>
       </c>
@@ -16627,8 +16901,11 @@
       <c r="H83" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I83" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>337</v>
       </c>
@@ -16653,8 +16930,11 @@
       <c r="H84" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I84" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>224</v>
       </c>
@@ -16679,8 +16959,11 @@
       <c r="H85" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I85" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>277</v>
       </c>
@@ -16705,8 +16988,11 @@
       <c r="H86" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I86" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>235</v>
       </c>
@@ -16731,8 +17017,11 @@
       <c r="H87" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I87" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>332</v>
       </c>
@@ -16757,8 +17046,11 @@
       <c r="H88" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I88" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>284</v>
       </c>
@@ -16783,8 +17075,11 @@
       <c r="H89" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I89" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>358</v>
       </c>
@@ -16809,8 +17104,11 @@
       <c r="H90" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I90" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>166</v>
       </c>
@@ -16835,8 +17133,11 @@
       <c r="H91" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I91" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>115</v>
       </c>
@@ -16861,8 +17162,11 @@
       <c r="H92" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I92" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>247</v>
       </c>
@@ -16887,8 +17191,11 @@
       <c r="H93" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I93" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>200</v>
       </c>
@@ -16913,8 +17220,11 @@
       <c r="H94" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I94" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>146</v>
       </c>
@@ -16939,8 +17249,11 @@
       <c r="H95" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I95" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>203</v>
       </c>
@@ -16965,8 +17278,11 @@
       <c r="H96" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I96" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>125</v>
       </c>
@@ -16991,8 +17307,11 @@
       <c r="H97" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I97" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>149</v>
       </c>
@@ -17017,8 +17336,11 @@
       <c r="H98" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I98" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>253</v>
       </c>
@@ -17043,8 +17365,11 @@
       <c r="H99" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I99" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>226</v>
       </c>
@@ -17069,8 +17394,11 @@
       <c r="H100" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I100" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>133</v>
       </c>
@@ -17095,8 +17423,11 @@
       <c r="H101" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I101" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>158</v>
       </c>
@@ -17121,8 +17452,11 @@
       <c r="H102" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I102" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>67</v>
       </c>
@@ -17147,8 +17481,11 @@
       <c r="H103" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I103" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>283</v>
       </c>
@@ -17173,8 +17510,11 @@
       <c r="H104" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I104" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>189</v>
       </c>
@@ -17199,8 +17539,11 @@
       <c r="H105" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I105" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>269</v>
       </c>
@@ -17225,8 +17568,11 @@
       <c r="H106" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I106" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>313</v>
       </c>
@@ -17251,8 +17597,11 @@
       <c r="H107" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I107" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>102</v>
       </c>
@@ -17277,8 +17626,11 @@
       <c r="H108" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I108" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>177</v>
       </c>
@@ -17303,8 +17655,11 @@
       <c r="H109" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I109" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>161</v>
       </c>
@@ -17329,8 +17684,11 @@
       <c r="H110" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I110" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>242</v>
       </c>
@@ -17355,8 +17713,11 @@
       <c r="H111" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I111" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>72</v>
       </c>
@@ -17381,8 +17742,11 @@
       <c r="H112" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I112" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>388</v>
       </c>
@@ -17407,8 +17771,11 @@
       <c r="H113" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I113" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>192</v>
       </c>
@@ -17433,8 +17800,11 @@
       <c r="H114" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I114" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>216</v>
       </c>
@@ -17459,8 +17829,11 @@
       <c r="H115" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I115" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>282</v>
       </c>
@@ -17485,8 +17858,11 @@
       <c r="H116" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I116" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>335</v>
       </c>
@@ -17511,8 +17887,11 @@
       <c r="H117" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I117" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>279</v>
       </c>
@@ -17537,8 +17916,11 @@
       <c r="H118" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I118" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>127</v>
       </c>
@@ -17563,8 +17945,11 @@
       <c r="H119" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I119" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>118</v>
       </c>
@@ -17589,8 +17974,11 @@
       <c r="H120" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I120" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -17615,8 +18003,11 @@
       <c r="H121" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I121" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>264</v>
       </c>
@@ -17641,8 +18032,11 @@
       <c r="H122" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I122" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>190</v>
       </c>
@@ -17667,8 +18061,11 @@
       <c r="H123" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I123" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>163</v>
       </c>
@@ -17693,8 +18090,11 @@
       <c r="H124" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I124" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>108</v>
       </c>
@@ -17719,8 +18119,11 @@
       <c r="H125" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I125" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>85</v>
       </c>
@@ -17745,8 +18148,11 @@
       <c r="H126" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I126" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>218</v>
       </c>
@@ -17771,8 +18177,11 @@
       <c r="H127" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I127" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>394</v>
       </c>
@@ -17797,8 +18206,11 @@
       <c r="H128" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I128" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>27</v>
       </c>
@@ -17823,8 +18235,11 @@
       <c r="H129" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I129" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>276</v>
       </c>
@@ -17849,8 +18264,11 @@
       <c r="H130" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I130" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>170</v>
       </c>
@@ -17875,8 +18293,11 @@
       <c r="H131" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I131" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>144</v>
       </c>
@@ -17901,8 +18322,11 @@
       <c r="H132" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I132" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>361</v>
       </c>
@@ -17927,8 +18351,11 @@
       <c r="H133" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I133" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>79</v>
       </c>
@@ -17953,8 +18380,11 @@
       <c r="H134" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I134" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>168</v>
       </c>
@@ -17979,8 +18409,11 @@
       <c r="H135" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I135" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>278</v>
       </c>
@@ -18005,8 +18438,11 @@
       <c r="H136" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I136" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>207</v>
       </c>
@@ -18031,8 +18467,11 @@
       <c r="H137" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I137" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>219</v>
       </c>
@@ -18057,8 +18496,11 @@
       <c r="H138" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I138" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>233</v>
       </c>
@@ -18083,8 +18525,11 @@
       <c r="H139" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I139" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>176</v>
       </c>
@@ -18109,8 +18554,11 @@
       <c r="H140" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I140" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>180</v>
       </c>
@@ -18135,8 +18583,11 @@
       <c r="H141" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I141" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>196</v>
       </c>
@@ -18161,8 +18612,11 @@
       <c r="H142" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I142" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>137</v>
       </c>
@@ -18187,8 +18641,11 @@
       <c r="H143" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I143" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>209</v>
       </c>
@@ -18213,8 +18670,11 @@
       <c r="H144" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I144" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>74</v>
       </c>
@@ -18239,8 +18699,11 @@
       <c r="H145" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I145" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>193</v>
       </c>
@@ -18265,8 +18728,11 @@
       <c r="H146" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I146" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>22</v>
       </c>
@@ -18291,8 +18757,11 @@
       <c r="H147" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I147" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>376</v>
       </c>
@@ -18317,8 +18786,11 @@
       <c r="H148" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I148" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>169</v>
       </c>
@@ -18343,8 +18815,11 @@
       <c r="H149" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I149" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>296</v>
       </c>
@@ -18369,8 +18844,11 @@
       <c r="H150" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I150" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>342</v>
       </c>
@@ -18395,8 +18873,11 @@
       <c r="H151" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I151" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>294</v>
       </c>
@@ -18421,8 +18902,11 @@
       <c r="H152" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I152" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>251</v>
       </c>
@@ -18447,8 +18931,11 @@
       <c r="H153" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I153" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>105</v>
       </c>
@@ -18473,8 +18960,11 @@
       <c r="H154" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I154" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>122</v>
       </c>
@@ -18499,8 +18989,11 @@
       <c r="H155" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I155" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>236</v>
       </c>
@@ -18525,8 +19018,11 @@
       <c r="H156" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I156" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>97</v>
       </c>
@@ -18551,8 +19047,11 @@
       <c r="H157" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I157" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>257</v>
       </c>
@@ -18577,8 +19076,11 @@
       <c r="H158" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I158" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>135</v>
       </c>
@@ -18603,8 +19105,11 @@
       <c r="H159" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I159" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>230</v>
       </c>
@@ -18629,8 +19134,11 @@
       <c r="H160" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I160" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>179</v>
       </c>
@@ -18655,8 +19163,11 @@
       <c r="H161" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I161" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>295</v>
       </c>
@@ -18681,8 +19192,11 @@
       <c r="H162" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I162" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>275</v>
       </c>
@@ -18707,8 +19221,11 @@
       <c r="H163" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I163" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>155</v>
       </c>
@@ -18733,8 +19250,11 @@
       <c r="H164" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I164" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>244</v>
       </c>
@@ -18759,8 +19279,11 @@
       <c r="H165" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I165" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>243</v>
       </c>
@@ -18785,8 +19308,11 @@
       <c r="H166" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I166" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>288</v>
       </c>
@@ -18811,8 +19337,11 @@
       <c r="H167" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I167" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>101</v>
       </c>
@@ -18837,8 +19366,11 @@
       <c r="H168" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I168" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>173</v>
       </c>
@@ -18863,8 +19395,11 @@
       <c r="H169" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I169" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>227</v>
       </c>
@@ -18889,8 +19424,11 @@
       <c r="H170" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I170" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>344</v>
       </c>
@@ -18915,8 +19453,11 @@
       <c r="H171" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I171" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>386</v>
       </c>
@@ -18941,8 +19482,11 @@
       <c r="H172" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I172" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>90</v>
       </c>
@@ -18967,8 +19511,11 @@
       <c r="H173" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I173" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>328</v>
       </c>
@@ -18993,8 +19540,11 @@
       <c r="H174" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I174" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>15</v>
       </c>
@@ -19016,8 +19566,11 @@
       <c r="G175" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I175" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>31</v>
       </c>
@@ -19039,8 +19592,11 @@
       <c r="G176" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I176" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>131</v>
       </c>
@@ -19062,8 +19618,11 @@
       <c r="G177" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I177" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>141</v>
       </c>
@@ -19085,8 +19644,11 @@
       <c r="G178" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I178" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>220</v>
       </c>
@@ -19107,6 +19669,9 @@
       </c>
       <c r="G179" t="s">
         <v>415</v>
+      </c>
+      <c r="I179" s="4" t="s">
+        <v>515</v>
       </c>
     </row>
   </sheetData>
